--- a/2. Proyectos/1. Interpreta Chile/Paginas Scraper.xlsx
+++ b/2. Proyectos/1. Interpreta Chile/Paginas Scraper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Jose Ordinola - Vault Projects\2. Proyectos\1. Interpreta Chile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724B1984-74DA-4B49-BA40-D7EB0D02F66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD8CAB9-D437-4905-9E91-EB0804D5C41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="3420" windowWidth="28800" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="110">
   <si>
     <t>CATEGORÍA</t>
   </si>
@@ -403,9 +403,6 @@
     <t>https://www.facebook.com/share/v/1AojFKSKyQ/</t>
   </si>
   <si>
-    <t>publicaciones</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/reel/DJFjzGSPmoW/?igsh=bTI2bzM4NWJrczdh</t>
   </si>
   <si>
@@ -434,6 +431,21 @@
   </si>
   <si>
     <t>Apify</t>
+  </si>
+  <si>
+    <t>carolina_toha</t>
+  </si>
+  <si>
+    <t>jeannettejararoman</t>
+  </si>
+  <si>
+    <t>gonzalo.winter</t>
+  </si>
+  <si>
+    <t>joukaiser</t>
+  </si>
+  <si>
+    <t>publicaciones/comentarios</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +1762,7 @@
     <col min="1" max="1" width="32.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="62" style="2" customWidth="1"/>
     <col min="3" max="3" width="25.5703125" style="2" customWidth="1"/>
-    <col min="4" max="8" width="22.42578125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="24" style="6" customWidth="1"/>
     <col min="9" max="9" width="23.85546875" style="2" customWidth="1"/>
     <col min="10" max="16384" width="10.7109375" style="2"/>
   </cols>
@@ -1804,19 +1816,19 @@
         <v>70</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>7</v>
@@ -1833,19 +1845,19 @@
         <v>71</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>7</v>
@@ -1862,19 +1874,19 @@
         <v>72</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>7</v>
@@ -1891,19 +1903,19 @@
         <v>73</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>7</v>
@@ -1920,19 +1932,19 @@
         <v>74</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>7</v>
@@ -1949,19 +1961,19 @@
         <v>75</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>7</v>
@@ -1975,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>59</v>
@@ -2003,6 +2015,24 @@
       <c r="B11" s="13" t="s">
         <v>5</v>
       </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -2011,6 +2041,24 @@
       <c r="B12" s="13" t="s">
         <v>9</v>
       </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -2019,6 +2067,24 @@
       <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
+      <c r="C13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -2027,6 +2093,24 @@
       <c r="B14" s="13" t="s">
         <v>15</v>
       </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -2035,6 +2119,24 @@
       <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
@@ -2042,6 +2144,24 @@
       </c>
       <c r="B16" s="13" t="s">
         <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2293,7 +2413,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2301,7 +2421,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2309,7 +2429,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2317,7 +2437,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2341,7 +2461,7 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2349,7 +2469,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2357,7 +2477,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2365,7 +2485,7 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,7 +2493,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
